--- a/program_log.xlsx
+++ b/program_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -637,6 +637,74 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-18 11:21:47</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>clean_doc.txt</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>안전</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-18 11:21:49</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>malware_01.txt</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>위험(격리)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-18 11:21:51</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>normal_photo.png</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>안전</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-18 11:21:52</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>suspicious_script.py</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>안전</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
